--- a/output/laminas_comunales/comunal_o_ocup_a_2023_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,142 +384,1042 @@
         </is>
       </c>
       <c r="C2">
-        <v>62.8156565656566</v>
+        <v>84.1666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Torres del Paine</t>
+          <t>Timaukel</t>
         </is>
       </c>
       <c r="C3">
-        <v>52.2313296903461</v>
+        <v>71.1538461538462</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timaukel</t>
+          <t>Laguna Blanca</t>
         </is>
       </c>
       <c r="C4">
-        <v>50.9887005649718</v>
+        <v>69.08602150537639</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Laguna Blanca</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="C5">
-        <v>46.7222222222222</v>
+        <v>67.9012345679012</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Torres del Paine</t>
         </is>
       </c>
       <c r="C6">
-        <v>46.3235688609904</v>
+        <v>67.43827160493829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Gregorio</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="C7">
-        <v>44.1624365482233</v>
+        <v>67.1146953405018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="C8">
-        <v>44.034302759135</v>
+        <v>63.7595907928389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="C9">
-        <v>41.6887883649515</v>
+        <v>62.8156565656566</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Laguna Blanca</t>
         </is>
       </c>
       <c r="C10">
-        <v>40.2119252873563</v>
+        <v>61.8518518518519</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>61.3707165109034</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>60.7142857142857</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>59.4594594594595</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>59.0132151429091</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>58.3979328165375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>57.7283511269276</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>57.1882766563618</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>57.1316409316933</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>56.3541666666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>55.3571428571429</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>55.2742616033755</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>53.3333333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>52.6729559748428</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>52.5641025641026</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>52.2313296903461</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>50.9887005649718</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>50.1282051282051</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>12201</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Cabo de Hornos</t>
         </is>
       </c>
-      <c r="C11">
+      <c r="C29">
+        <v>49.6478873239437</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>49.6376811594203</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>49.6153846153846</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>48.8955823293173</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>48.0694215883464</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>47.6584022038568</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>47.0201427593625</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>46.7222222222222</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>46.3235688609904</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>45.4766999524489</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>44.9555361238059</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>44.1624365482233</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>44.034302759135</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>42.2132658974764</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>41.6887883649515</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>41.4634146341463</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>40.4712643678161</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>40.2119252873563</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>39.6898432174506</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>39.6727172717272</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>39.3963580465886</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>38.8888888888889</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>38.5964912280702</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>38.4057910939408</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>38.0905511811024</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C54">
         <v>36.8615147512109</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>35.7142857142857</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>35.5614973262032</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>34.2951858976686</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>33.8888888888889</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>33.5445711871567</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>33.3333333333333</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Río Verde</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>30.5555555555556</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>30.4254488680718</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>24.8062015503876</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>24.4764397905759</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12402</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Torres del Paine</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>22.7272727272727</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>21.9827586206897</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>12104</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>San Gregorio</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>21.7687074829932</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>12303</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Timaukel</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>20.3703703703704</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>17.7269345238095</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>15.248371778954</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>11.7731116943715</v>
       </c>
     </row>
   </sheetData>
